--- a/partner_results/dik/ClassMissingGermanDefinition_dik.xlsx
+++ b/partner_results/dik/ClassMissingGermanDefinition_dik.xlsx
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mixing chamber temperature control unit [dik]</t>
+          <t>electrical power [dik]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>extensive quality</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -459,13 +459,17 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mass temperature [dik]</t>
+          <t>haul-off speed [dik]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -480,7 +484,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The temperature of the bulk polymer material (polymer melt, rubber compound, or mixture) during processing, representing the average thermal state of the material mass rather than the temperature of surrounding equipment surfaces.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -501,18 +505,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>drop door temperature control unit [dik]</t>
+          <t>torque unit [dik]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>measurement unit label</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>drop door temperature control unit</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -530,7 +538,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>product data sheet [dik]</t>
+          <t>safety data sheet [dik]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -543,18 +551,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ethylene concentration measurement assay [dik]</t>
+          <t>Newtonmeter [dik]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>assay</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -564,7 +576,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A concentration measurement assay with the objective to produce information about the concentration of ethylene in the material entity that is the evaluant, by physically examining it or its proxies.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -572,12 +584,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rotor speed [dik]</t>
+          <t>ethylidene norbornene [dik]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>chemical substance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -585,18 +597,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quality of a liquid [dik]</t>
+          <t>rotational frequency [dik]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -604,18 +620,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A physical quality which inheres in a bearer by virtue of its speed rotating around itself.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>die geometry [dik]</t>
+          <t>screw speed [dik]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>geometry [imr]</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -623,18 +643,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pressure variation [dik]</t>
+          <t>setting roll speed [dik]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>process attribute</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -644,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pressure variation refers to the change in pressure within a fluid as a function of depth, position, and time, influenced by factors such as fluid density and gravitational force.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -652,12 +676,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dithiocarbamate [dik]</t>
+          <t>ethylene concentration [dik]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dithiocarbamate anions</t>
+          <t>concentration [dik]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -665,18 +689,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A concentration of ethylene inhering in a substance by virtue of the amount of the bearer's there is mixed with ethylene.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>drop door temperature [dik]</t>
+          <t>ethylene concentration measurement protocol [dik]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>measurement protocol [dik]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -684,18 +712,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A concentration measurement protocol for reliably reproducing the ethylene concentration measurement assay.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organodiyl group [dik]</t>
+          <t>quality of a solid [dik]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>organic divalent group [chebi]</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -703,18 +735,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rotor temperature control unit [dik]</t>
+          <t>concentration measurement protocol [dik]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>measurement protocol [dik]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -722,18 +758,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A measurement protocol for reliably reproducing the concentration measurement assay.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>screw speed [dik]</t>
+          <t>optical quality [dik]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -741,18 +781,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pin zone temperature [dik]</t>
+          <t>time of addition [dik]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>temporal interval</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -760,18 +804,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>material processing [dik]</t>
+          <t>Mooney viscosity measurement assay [dik]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>assay</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -779,18 +827,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>An assay with the objective to produce information about the Mooney viscosity of the material entity that is the evaluant, by physically examining it or its proxies.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>density measurement protocol [dik]</t>
+          <t>drop door [dik]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>measurement protocol [dik]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -800,7 +852,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A measurement protocol for reliably reproducing the density measurement assay.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -808,12 +860,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>concentration measurement protocol [dik]</t>
+          <t>setting roll temperature [dik]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>measurement protocol [dik]</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -823,7 +875,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A measurement protocol for reliably reproducing the concentration measurement assay.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -831,12 +883,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>extrudate cross section [dik]</t>
+          <t>setting roll temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fiat object part</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -844,13 +896,17 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>setting roll [dik]</t>
+          <t>rotor temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -863,18 +919,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>number of mixing stages [dik]</t>
+          <t>pressure variation [dik]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>measurement datum</t>
+          <t>process attribute</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -882,13 +942,17 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Pressure variation refers to the change in pressure within a fluid as a function of depth, position, and time, influenced by factors such as fluid density and gravitational force.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>viscometer [dik]</t>
+          <t>rotor [dik]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -901,18 +965,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ethylidene norbornene concentration measurement assay [dik]</t>
+          <t>stamp temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>assay</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -922,7 +990,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A concentration measurement assay with the objective to produce information about the concentration of ethylidene norbornene in the material entity that is the evaluant, by physically examining it or its proxies.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -930,12 +998,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>setting point [dik]</t>
+          <t>ethylene concentration measurement assay [dik]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>assay</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -943,37 +1011,41 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A concentration measurement assay with the objective to produce information about the concentration of ethylene in the material entity that is the evaluant, by physically examining it or its proxies.</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>single screw extruder [dik]</t>
+          <t>physical quality [dik]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>extruder</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hydrocarbylene group [dik]</t>
+          <t>fixed roll temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>organodiyl group [chebi]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -981,18 +1053,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>torque unit [dik]</t>
+          <t>Mooney shearing-disc viscometer [dik]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>measurement unit label</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1000,18 +1076,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>safety data sheet [dik]</t>
+          <t>hydrocarbylene group [dik]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>organodiyl group [chebi]</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1019,18 +1099,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>rotational frequency [dik]</t>
+          <t>pin zone temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1040,7 +1124,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A physical quality which inheres in a bearer by virtue of its speed rotating around itself.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1048,12 +1132,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>vulcanization time [dik]</t>
+          <t>number of mixing stages [dik]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>temporal interval</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1061,20 +1145,24 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>density measurement protocol [dik]</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>measurement protocol [dik]</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>protocol [obi]</t>
-        </is>
-      </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>Alexander Aschemann</t>
@@ -1082,7 +1170,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A protocol which specifies the conditions, procedures, and instruments used for conducting a measurement assay in a sufficient level of detail to communicate it between investigation agents, so that different investigation agents will reliably be able to independently reproduce the measurement assay.</t>
+          <t>A measurement protocol for reliably reproducing the density measurement assay.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1090,12 +1178,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>specific surface [dik]</t>
+          <t>organic divalent group [dik]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>surface [dik]</t>
+          <t>organic group [chebi]</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1103,156 +1191,184 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>vulcanization time [dik]</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>temporal interval</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>melting range [dik]</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>torque [dik]</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>extensive quality</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>rotor torque [dik]</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>device specification</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>setting roll [dik]</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>quality of a substance [dik]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>stearic acid [dik]</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>pure substance</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Stearic acid is a common 18-carbon long-chain saturated fatty acid (
 ) found widely in animal and vegetable fats.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Newtonmeter [dik]</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>device</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>molding zone temperature control unit [dik]</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>device</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>screw temperature [dik]</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>device specification</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Mooney unit [dik]</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>measurement unit label</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>fixed roll temperature [dik]</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>stamp distance [dik]</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>plan specification</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mooney viscosity measurement protocol [dik]</t>
+          <t>temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>measurement protocol [dik]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1262,7 +1378,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A viscosity measurement protocol for reliably reproducing the Mooney viscosity measurement assay.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1270,31 +1386,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>feeding zone temperature [dik]</t>
+          <t>ethylidene group [dik]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>intensive quality</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>organodiyl group [chebi]</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>volume-specific surface [dik]</t>
+          <t>ethylidene norbornene concentration measurement assay [dik]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>surface [dik]</t>
+          <t>assay</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1302,18 +1418,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>A concentration measurement assay with the objective to produce information about the concentration of ethylidene norbornene in the material entity that is the evaluant, by physically examining it or its proxies.</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>fixed roll [dik]</t>
+          <t>molecular weight distribution measurement assay [dik]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>assay</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1321,18 +1441,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>An assay with the objective to produce information about the molecular weight distribution of the material entity that is the evaluant, by physically examining it or its proxies.</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mass throughput [dik]</t>
+          <t>fixed roll [dik]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>extensive quality</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1342,7 +1466,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>In polymers, mass throughput is the mass of polymer material that passes through a processing unit (e.g., extruder, mixer, or die) per unit time.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -1350,12 +1474,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mixing [dik]</t>
+          <t>feeding roll temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>planned process</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1363,18 +1487,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>engine [dik]</t>
+          <t>measurement protocol [dik]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>protocol [obi]</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1382,18 +1510,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>A protocol which specifies the conditions, procedures, and instruments used for conducting a measurement assay in a sufficient level of detail to communicate it between investigation agents, so that different investigation agents will reliably be able to independently reproduce the measurement assay.</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>torque [dik]</t>
+          <t>pin extruder [dik]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>extensive quality</t>
+          <t>extruder</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1401,18 +1533,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>molecular weight distribution measurement assay [dik]</t>
+          <t>drop door temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>assay</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1422,7 +1558,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>An assay with the objective to produce information about the molecular weight distribution of the material entity that is the evaluant, by physically examining it or its proxies.</t>
+          <t>drop door temperature control unit</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -1430,31 +1566,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rotor temperature [dik]</t>
+          <t>function [dik]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>device specification</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>oil content [dik]</t>
+          <t>mixing chamber [dik]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1462,18 +1598,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>conveyor belt [dik]</t>
+          <t>setting point [dik]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1481,18 +1621,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>concentration measurement assay [dik]</t>
+          <t>mass throughput [dik]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>assay</t>
+          <t>extensive quality</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1502,7 +1646,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>An assay with the objective to produce information about the concentration of a specific substance in the material entity that is the evaluant, by physically examining it or its proxies.</t>
+          <t>In polymers, mass throughput is the mass of polymer material that passes through a processing unit (e.g., extruder, mixer, or die) per unit time.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -1510,12 +1654,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>setting roll temperature control unit [dik]</t>
+          <t>die geometry [dik]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>geometry [imr]</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1523,33 +1667,45 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>function [dik]</t>
+          <t>di(benzothiazol-2-yl)disulfide [dik]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>function</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+          <t>organic disulfide</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>sulfur [dik]</t>
+          <t>extrudate cross section [dik]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>pure substance</t>
+          <t>fiat object part</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1559,7 +1715,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sulfur is the chemical element of atomic number 16, a yellow combustible non-metal.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -1567,27 +1723,35 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ethylidene group [dik]</t>
+          <t>mixing [dik]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>organodiyl group [chebi]</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>planned process</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>melting range [dik]</t>
+          <t>organodiyl group [dik]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>organic divalent group [chebi]</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1595,33 +1759,45 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>physical quality [dik]</t>
+          <t>viscometer [dik]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>quality</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>electrical power [dik]</t>
+          <t>viscosity measurement protocol [dik]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>extensive quality</t>
+          <t>measurement protocol [dik]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1629,37 +1805,41 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>A measurement protocol for reliably reproducing the viscosity measurement assay.</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pressure Sensor [dik]</t>
+          <t>zinc oxide [dik]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>sensor [chmo]</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>chemical substance</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>stamp [dik]</t>
+          <t>feeding zone temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>polymer [chebi]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1669,7 +1849,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>In polymer mixing, a stamp is defined as a polymer material that is used to create patterns or shapes on a surface.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1677,12 +1857,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ethylene concentration [dik]</t>
+          <t>mixing chamber temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>concentration [dik]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1692,7 +1872,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>A concentration of ethylene inhering in a substance by virtue of the amount of the bearer's there is mixed with ethylene.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -1700,12 +1880,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>organic divalent group [dik]</t>
+          <t>drop door temperature [dik]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>organic group [chebi]</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1713,13 +1893,17 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>viscosity measurement protocol [dik]</t>
+          <t>ethylidene norbornene concentration measurement protocol [dik]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1734,7 +1918,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>A measurement protocol for reliably reproducing the viscosity measurement assay.</t>
+          <t>A concentration measurement protocol for reliably reproducing the ethylidene norbornene concentration measurement assay.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -1742,12 +1926,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>zinc dibenzyldithiocarbamate [dik]</t>
+          <t>concentration measurement assay [dik]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>vulcanisation accelerator [dik]</t>
+          <t>assay</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1755,18 +1939,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>An assay with the objective to produce information about the concentration of a specific substance in the material entity that is the evaluant, by physically examining it or its proxies.</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>surface defect [dik]</t>
+          <t>temperature sensor [dik]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>sensor [chmo]</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1774,18 +1962,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>mixing chamber temperature [dik]</t>
+          <t>screw temperature [dik]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1793,18 +1985,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>quality of a solid [dik]</t>
+          <t>filling ratio [dik]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1812,18 +2008,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>A physical quality which inheres in a bearer by virtue of the ratio of the volume of a substance contained in the bearer and the bearer's own volume.</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>mixing chamber [dik]</t>
+          <t>quality of a liquid [dik]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1831,18 +2031,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>quality of a substance [dik]</t>
+          <t>temperature measuring sword [dik]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1850,18 +2054,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>group [dik]</t>
+          <t>fixed roll temperature [dik]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>chemical entity</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1869,13 +2077,17 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>fixed roll temperature control unit [dik]</t>
+          <t>feeding roll [dik]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1888,18 +2100,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>filling ratio [dik]</t>
+          <t>curemeter [dik]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1909,7 +2125,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>A physical quality which inheres in a bearer by virtue of the ratio of the volume of a substance contained in the bearer and the bearer's own volume.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -1917,12 +2133,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>molecular weight distribution measurement protocol [dik]</t>
+          <t>mixing chamber temperature [dik]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>protocol [obi]</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1932,7 +2148,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>A measurement protocol for reliably reproducing the molecular weight distribution measurement assay.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -1940,12 +2156,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>screw temperature control unit [dik]</t>
+          <t>material processing [dik]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1953,13 +2169,17 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>stamp temperature [dik]</t>
+          <t>concentration [dik]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1972,18 +2192,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>setting roll temperature [dik]</t>
+          <t>surface [dik]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>surface layer (fiat object part)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1991,18 +2215,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>material processing protocol [dik]</t>
+          <t>sulfur [dik]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>protocol [obi]</t>
+          <t>pure substance</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2012,7 +2240,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>A protocol which specifies the conditions, procedures, and instruments used for conducting a material processing in a sufficient level of detail to communicate it between investigation agents, so that different investigation agents will reliably be able to independently reproduce the material processing.</t>
+          <t>Sulfur is the chemical element of atomic number 16, a yellow combustible non-metal.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2020,12 +2248,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mooney shearing-disc viscometer [dik]</t>
+          <t>product data sheet [dik]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2033,13 +2261,17 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>feeding roll temperature control unit [dik]</t>
+          <t>conveyor belt [dik]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2052,18 +2284,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>temperature measuring sword [dik]</t>
+          <t>mixing time [dik]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>temporal interval</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2071,18 +2307,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>setting roll speed [dik]</t>
+          <t>surface defect [dik]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2090,18 +2330,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>pin extruder [dik]</t>
+          <t>zinc dibenzyldithiocarbamate [dik]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>extruder</t>
+          <t>vulcanisation accelerator [dik]</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2109,18 +2353,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ethylidene norbornene concentration measurement protocol [dik]</t>
+          <t>viscosity measurement assay [dik]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>measurement protocol [dik]</t>
+          <t>assay</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2130,7 +2378,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>A concentration measurement protocol for reliably reproducing the ethylidene norbornene concentration measurement assay.</t>
+          <t>An assay with the objective to produce information about the viscosity of the material entity that is the evaluant, by physically examining it or its proxies.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2138,12 +2386,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>processed material [dik]</t>
+          <t>single screw extruder [dik]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>extruder</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2151,18 +2399,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mass-specific surface [dik]</t>
+          <t>rotor temperature [dik]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2172,7 +2424,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>The total surface area of a material divided by its mass.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2180,12 +2432,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>manufacturing specification [dik]</t>
+          <t>engine [dik]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2193,18 +2445,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>temperature sensor [dik]</t>
+          <t>rotor speed [dik]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>sensor [chmo]</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2212,18 +2468,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ethylene concentration measurement protocol [dik]</t>
+          <t>manufacturing specification [dik]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>measurement protocol [dik]</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2233,7 +2493,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>A concentration measurement protocol for reliably reproducing the ethylene concentration measurement assay.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2254,18 +2514,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>curemeter [dik]</t>
+          <t>oil content [dik]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2273,18 +2537,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>gearbox [dik]</t>
+          <t>dithiocarbamate [dik]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dithiocarbamate anions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2292,18 +2560,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>surface [dik]</t>
+          <t>feeding zone temperature [dik]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>surface layer (fiat object part)</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2311,18 +2583,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>geometry variation [dik]</t>
+          <t>mass-specific surface [dik]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>process attribute</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2332,7 +2608,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Geometry variation refers to the distortion and rearrangement of polymer chains due to various factors such as temperature, pressure and external forces that can lead to changes in the polymer's physical properties such as viscosity, strength and flexibility.</t>
+          <t>The total surface area of a material divided by its mass.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -2340,7 +2616,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>optical quality [dik]</t>
+          <t>pin zone temperature [dik]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2353,18 +2629,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mixing time [dik]</t>
+          <t>density measurement assay [dik]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>temporal interval</t>
+          <t>assay</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2372,18 +2652,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>An assay with the objective to produce information about the density of the material entity that is the evaluant, by physically examining it or its proxies.</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>rotor [dik]</t>
+          <t>stamp temperature [dik]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2391,18 +2675,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>molding zone temperature [dik]</t>
+          <t>ethylidene norbornene concentration [dik]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>concentration [dik]</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2410,7 +2698,11 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>A concentration of ethylidene norbornene inhering in a substance by virtue of the amount of the bearer's there is mixed with ethylidene norbornene.</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
@@ -2429,18 +2721,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>stamp temperature control unit [dik]</t>
+          <t>geometry variation [dik]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>process attribute</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2448,18 +2744,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Geometry variation refers to the distortion and rearrangement of polymer chains due to various factors such as temperature, pressure and external forces that can lead to changes in the polymer's physical properties such as viscosity, strength and flexibility.</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rotor torque [dik]</t>
+          <t>screw temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2467,18 +2767,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>feeding roll [dik]</t>
+          <t>processed material [dik]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2486,18 +2790,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>viscosity measurement assay [dik]</t>
+          <t>molecular weight distribution measurement protocol [dik]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>assay</t>
+          <t>protocol [obi]</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2507,7 +2815,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>An assay with the objective to produce information about the viscosity of the material entity that is the evaluant, by physically examining it or its proxies.</t>
+          <t>A measurement protocol for reliably reproducing the molecular weight distribution measurement assay.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -2515,12 +2823,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ethylidene norbornene [dik]</t>
+          <t>fixed roll speed [dik]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2528,18 +2836,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>pin zone temperature control unit [dik]</t>
+          <t>group [dik]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>chemical entity</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2547,18 +2859,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>time of addition [dik]</t>
+          <t>molding zone temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>temporal interval</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2566,33 +2882,45 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>zinc oxide [dik]</t>
+          <t>mass temperature [dik]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>chemical substance</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>The temperature of the bulk polymer material (polymer melt, rubber compound, or mixture) during processing, representing the average thermal state of the material mass rather than the temperature of surrounding equipment surfaces.</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>concentration [dik]</t>
+          <t>specific surface [dik]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>surface [dik]</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2600,18 +2928,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>surface temperature [dik]</t>
+          <t>Mooney unit [dik]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>measurement unit label</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2619,18 +2951,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mooney viscosity measurement assay [dik]</t>
+          <t>stamp distance [dik]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>assay</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2640,7 +2976,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>An assay with the objective to produce information about the Mooney viscosity of the material entity that is the evaluant, by physically examining it or its proxies.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -2648,12 +2984,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ethylene group [dik]</t>
+          <t>material processing protocol [dik]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>hydrocarbylene group [chebi]</t>
+          <t>protocol [obi]</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2661,18 +2997,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>A protocol which specifies the conditions, procedures, and instruments used for conducting a material processing in a sufficient level of detail to communicate it between investigation agents, so that different investigation agents will reliably be able to independently reproduce the material processing.</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>di(benzothiazol-2-yl)disulfide [dik]</t>
+          <t>Pressure Sensor [dik]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>organic disulfide</t>
+          <t>sensor [chmo]</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2680,18 +3020,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>density measurement assay [dik]</t>
+          <t>stamp [dik]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>assay</t>
+          <t>polymer [chebi]</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2701,7 +3045,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>An assay with the objective to produce information about the density of the material entity that is the evaluant, by physically examining it or its proxies.</t>
+          <t>In polymer mixing, a stamp is defined as a polymer material that is used to create patterns or shapes on a surface.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -2709,12 +3053,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>thiuram [dik]</t>
+          <t>Mooney viscosity measurement protocol [dik]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>vulcanisation accelerator [dik]</t>
+          <t>measurement protocol [dik]</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2722,13 +3066,17 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>A viscosity measurement protocol for reliably reproducing the Mooney viscosity measurement assay.</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>haul-off speed [dik]</t>
+          <t>molding zone temperature [dik]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2741,18 +3089,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>drop door [dik]</t>
+          <t>volume-specific surface [dik]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>surface [dik]</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2760,13 +3112,17 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>feeding zone temperature control unit [dik]</t>
+          <t>gearbox [dik]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2779,18 +3135,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>temperature control unit [dik]</t>
+          <t>ethylene group [dik]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>hydrocarbylene group [chebi]</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2798,18 +3158,22 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>fixed roll speed [dik]</t>
+          <t>thiuram [dik]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>vulcanisation accelerator [dik]</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2817,13 +3181,17 @@
           <t>Alexander Aschemann</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ethylidene norbornene concentration [dik]</t>
+          <t>surface temperature [dik]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2838,7 +3206,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>A concentration of ethylidene norbornene inhering in a substance by virtue of the amount of the bearer's there is mixed with ethylidene norbornene.</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
